--- a/data/target_form/신김포농협.xlsx
+++ b/data/target_form/신김포농협.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae7f7f815e37025b/문서/365건강농산/목표양식/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skawl\PycharmProjects\365배포\data\target_form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7ED820E1-06A2-42D8-811C-F380E827C7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B972CD-0FA6-458B-BDC4-C984FB2FBD91}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89257EF-0CD9-490C-8E9F-38F95591BAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>수량</t>
   </si>
@@ -79,31 +79,27 @@
     <t>택배사코드(필수)</t>
   </si>
   <si>
-    <t>수신 : 신김포농협미곡종합처리장</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>신김포농협 고시히카리 쌀10kg</t>
   </si>
   <si>
     <t>이상희</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>010-2886-9503</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>충북 음성군 삼성면 덕정로110-1 하늬하이츠 1동 302호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>김형영</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>010-2351-7863</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -115,7 +111,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -123,14 +119,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -203,7 +191,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -226,22 +214,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -251,31 +230,28 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -590,7 +566,7 @@
   <sheetPr codeName="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -609,114 +585,100 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-    </row>
-    <row r="2" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="D2" s="8">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="E2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="8">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-    </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="10">
+      <c r="B3" s="10">
         <v>46013</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:H1"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -728,7 +690,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" draft="1"/>
 </worksheet>
@@ -740,7 +702,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" draft="1"/>
 </worksheet>
@@ -752,7 +714,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
